--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-LST-01_ekipman_envanteri_ve_abc_kritiklik_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-LST-01_ekipman_envanteri_ve_abc_kritiklik_listesi.xlsx
@@ -762,7 +762,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-LST-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Envanteri ve ABC Kritiklik Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Ekipman kritiklik sınıfları güvenlik ve ürün etkisine bağlandı; envanter ve bakım planı bağı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -972,7 +973,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-LST-01&amp;C&amp;"Arial,Regular"&amp;11Ekipman Envanteri ve ABC Kritiklik Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Ekipman kritiklik sınıfları güvenlik ve ürün etkisine bağlandı; envanter ve bakım planı bağı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>